--- a/MERIX SUBMISSION/M06-2_XML_WebViz/exports/score_pdf_long/pdf/评估/乐句断句评审表.xlsx
+++ b/MERIX SUBMISSION/M06-2_XML_WebViz/exports/score_pdf_long/pdf/评估/乐句断句评审表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toddywang/Documents/VsCodeProjects/xmltoexp/MERIX SUBMISSION/M06-2_XML_WebViz/exports/score_pdf_long/pdf/评估/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E9872D-658C-994B-9528-AE503D3D01FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84DBAAD-CA27-5A47-92AB-15F4436BD2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20580" yWindow="540" windowWidth="17820" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20580" yWindow="500" windowWidth="17820" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="选项" sheetId="2" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="M06-3" sheetId="17" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'M06-1'!$A$3:$G$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'M06-2'!$A$3:$G$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'M06-3'!$A$3:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'M06-1'!$A$3:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'M06-2'!$A$3:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'M06-3'!$A$3:$G$109</definedName>
     <definedName name="judgment_options">选项!$A$2:$A$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="66">
   <si>
     <t>判断</t>
   </si>
@@ -157,6 +157,96 @@
   </si>
   <si>
     <t>m93b2</t>
+  </si>
+  <si>
+    <t>m9b1</t>
+  </si>
+  <si>
+    <t>m11b1</t>
+  </si>
+  <si>
+    <t>m13b1</t>
+  </si>
+  <si>
+    <t>m19b1</t>
+  </si>
+  <si>
+    <t>m22b3</t>
+  </si>
+  <si>
+    <t>m25b1</t>
+  </si>
+  <si>
+    <t>m29b1</t>
+  </si>
+  <si>
+    <t>m43b1</t>
+  </si>
+  <si>
+    <t>m75b3</t>
+  </si>
+  <si>
+    <t>若新增位置，没标代表其他人在此处没有标记</t>
+  </si>
+  <si>
+    <t>有编号位置，没标代表可视为</t>
+  </si>
+  <si>
+    <t>m98b3</t>
+  </si>
+  <si>
+    <t>m5b2</t>
+  </si>
+  <si>
+    <t>m7b2</t>
+  </si>
+  <si>
+    <t>m11b2</t>
+  </si>
+  <si>
+    <t>m20b1</t>
+  </si>
+  <si>
+    <t>m21b2</t>
+  </si>
+  <si>
+    <t>m26b1</t>
+  </si>
+  <si>
+    <t>m34b3</t>
+  </si>
+  <si>
+    <t>m36b1</t>
+  </si>
+  <si>
+    <t>m38b1</t>
+  </si>
+  <si>
+    <t>m42b1</t>
+  </si>
+  <si>
+    <t>m52b1</t>
+  </si>
+  <si>
+    <t>m54b1</t>
+  </si>
+  <si>
+    <t>m58b1</t>
+  </si>
+  <si>
+    <t>m70b1</t>
+  </si>
+  <si>
+    <t>m73b2</t>
+  </si>
+  <si>
+    <t>m77b2</t>
+  </si>
+  <si>
+    <t>m79b2</t>
+  </si>
+  <si>
+    <t>m10b1</t>
   </si>
 </sst>
 </file>
@@ -223,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -242,6 +332,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -576,19 +669,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E874A1B1-FC00-764C-9222-91C2AE8AA66D}">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
@@ -597,6 +691,9 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
       <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
@@ -634,7 +731,9 @@
       <c r="D4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
@@ -650,7 +749,9 @@
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
@@ -666,7 +767,9 @@
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
@@ -724,153 +827,155 @@
       <c r="D10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>5</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4">
-        <v>3</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="4"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4">
-        <v>3</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <v>5</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
-        <v>9</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4">
-        <v>2</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C16" s="4">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <v>3</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
-        <v>12</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
-        <v>3</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F20" s="4"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
@@ -882,66 +987,70 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
-        <v>16</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4">
-        <v>5</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="4"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4">
-        <v>4</v>
-      </c>
-      <c r="D23" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
-        <v>18</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
         <v>3</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F25" s="4"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -949,83 +1058,81 @@
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
-        <v>21</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F27" s="4"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
         <v>3</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <v>3</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F29" s="4"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C30" s="4">
+        <v>4</v>
+      </c>
+      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
         <v>3</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
+      <c r="C32" s="4">
+        <v>3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1034,7 +1141,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4">
@@ -1047,48 +1154,52 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="4">
-        <v>5</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F34" s="4"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
-        <v>4</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F35" s="4"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>30</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4">
-        <v>3</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F36" s="4"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
@@ -1101,25 +1212,31 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="4">
-        <v>3</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="4"/>
+      <c r="A39" s="4">
+        <v>25</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4">
+        <v>3</v>
+      </c>
       <c r="D39" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -1127,11 +1244,11 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="4">
-        <v>3</v>
+      <c r="C40" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -1140,65 +1257,61 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <v>1</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <v>3</v>
-      </c>
-      <c r="D42" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C43" s="4">
+        <v>4</v>
+      </c>
+      <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C44" s="4">
+        <v>3</v>
+      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
@@ -1211,26 +1324,25 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
         <v>3</v>
       </c>
+      <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
-        <v>40</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4">
-        <v>5</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="4"/>
       <c r="D47" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -1238,65 +1350,69 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" s="4"/>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F48" s="4"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="4" t="s">
-        <v>20</v>
+      <c r="C49" s="4">
+        <v>1</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F49" s="4"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="4">
-        <v>5</v>
+      <c r="C51" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F51" s="4"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
@@ -1305,60 +1421,57 @@
       <c r="D52" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F52" s="4"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B53" s="4"/>
-      <c r="C53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C53" s="4">
+        <v>3</v>
+      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
-        <v>47</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4">
-        <v>5</v>
-      </c>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F54" s="4"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <v>4</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E55" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>3</v>
@@ -1366,182 +1479,246 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="1"/>
-      <c r="I56" s="3"/>
-    </row>
-    <row r="57" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="4">
-        <v>3</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F57" s="4"/>
       <c r="G57" s="1"/>
-      <c r="I57" s="5"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="4">
-        <v>3</v>
+      <c r="C58" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <v>3</v>
-      </c>
-      <c r="D60" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B61" s="4"/>
-      <c r="C61" s="4">
-        <v>1</v>
+      <c r="C61" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F61" s="4"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F62" s="4"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="4"/>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>47</v>
+      </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
+      <c r="C63" s="4">
+        <v>5</v>
+      </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" s="4"/>
+    <row r="64" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>48</v>
+      </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
+      <c r="C64" s="4">
+        <v>4</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F64" s="4"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
+    <row r="65" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>49</v>
+      </c>
       <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="7"/>
+      <c r="C65" s="4">
+        <v>4</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4"/>
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="1"/>
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>50</v>
+      </c>
       <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
+      <c r="C67" s="4">
+        <v>3</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="F67" s="4"/>
       <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="4"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>51</v>
+      </c>
       <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
+      <c r="C68" s="4">
+        <v>3</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="4"/>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>52</v>
+      </c>
       <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
+      <c r="C69" s="4">
+        <v>1</v>
+      </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="4"/>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>53</v>
+      </c>
       <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
+      <c r="C70" s="4">
+        <v>3</v>
+      </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>54</v>
+      </c>
       <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
+      <c r="C71" s="4">
+        <v>1</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="4"/>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>55</v>
+      </c>
       <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
+      <c r="C72" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -1550,7 +1727,7 @@
       <c r="F73" s="4"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -1559,52 +1736,52 @@
       <c r="F74" s="4"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="1"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="7"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="6"/>
+      <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="4"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -1671,27 +1848,27 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="1"/>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -1775,10 +1952,100 @@
       <c r="F98" s="4"/>
       <c r="G98" s="1"/>
     </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="1"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="1"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="1"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G98" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:G108" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="F67:F77 F79:F98 D79:D98 D67:D77 F4:F65 D61 D62:D65 D47 D4:D45 D48:D60" xr:uid="{C4C596A4-9E85-914E-B561-DE7166F64426}">
+    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D89:F108 D77:F87 D4:E54 F4:F57 E64:E66 D56:E63 D55 D68:E75 D64:D67 F59:F75" xr:uid="{C4C596A4-9E85-914E-B561-DE7166F64426}">
       <formula1>judgment_options</formula1>
     </dataValidation>
   </dataValidations>
@@ -1789,14 +2056,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4A3B48-98D7-2442-9DB5-64FBD8926EC0}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="40.33203125" customWidth="1"/>
   </cols>
@@ -1847,7 +2112,9 @@
       <c r="D4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1863,7 +2130,9 @@
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
@@ -1879,7 +2148,9 @@
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
@@ -1922,112 +2193,118 @@
         <v>5</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>4</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="4">
-        <v>2</v>
+      <c r="C10" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4">
-        <v>5</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>6</v>
-      </c>
+      <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4">
-        <v>2</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="4">
-        <v>5</v>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
         <v>2</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>10</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4">
-        <v>5</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
-        <v>20</v>
+      <c r="C17" s="4">
+        <v>5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2036,37 +2313,43 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4">
         <v>2</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
         <v>5</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="4">
-        <v>2</v>
+      <c r="C20" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -2075,39 +2358,39 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
-        <v>5</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F21" s="4"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
-        <v>16</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
-        <v>20</v>
+      <c r="C23" s="4">
+        <v>5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -2115,13 +2398,11 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
-        <v>18</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -2129,11 +2410,11 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
-        <v>20</v>
+      <c r="C25" s="4">
+        <v>2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -2142,65 +2423,69 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
         <v>5</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F27" s="4"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C28" s="4">
+        <v>2</v>
+      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="4">
-        <v>2</v>
+      <c r="C29" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F29" s="4"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -2209,65 +2494,71 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="4">
-        <v>5</v>
+      <c r="C31" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F31" s="4"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
         <v>5</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F32" s="4"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
-        <v>26</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4">
-        <v>2</v>
-      </c>
-      <c r="D33" s="4"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="4"/>
+      <c r="A34" s="4">
+        <v>21</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F34" s="4"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2275,38 +2566,38 @@
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>28</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4">
-        <v>5</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F36" s="4"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F37" s="4"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
-        <v>20</v>
+      <c r="C38" s="4">
+        <v>5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -2314,21 +2605,21 @@
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
-        <v>30</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4">
-        <v>2</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F39" s="4"/>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
@@ -2341,39 +2632,39 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
         <v>5</v>
       </c>
-      <c r="D41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>33</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4">
-        <v>5</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="4"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F42" s="4"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -2381,38 +2672,40 @@
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
-        <v>35</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="4"/>
       <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F44" s="4"/>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
-        <v>36</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4">
-        <v>3</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F45" s="4"/>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -2421,35 +2714,35 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
         <v>5</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F47" s="4"/>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
-        <v>39</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4">
-        <v>2</v>
-      </c>
-      <c r="D48" s="4"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
@@ -2460,22 +2753,22 @@
       <c r="F49" s="4"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
-        <v>41</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4">
-        <v>3</v>
-      </c>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F50" s="4"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
@@ -2486,63 +2779,61 @@
       <c r="F51" s="4"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
-        <v>43</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4">
-        <v>3</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="4"/>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F52" s="4"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
-        <v>45</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4">
-        <v>5</v>
-      </c>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F54" s="4"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
@@ -2551,110 +2842,114 @@
       <c r="D56" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E56" s="4"/>
+      <c r="E56" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F56" s="4"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>48</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4">
-        <v>2</v>
-      </c>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="4"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F57" s="4"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
+      <c r="E58" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F58" s="4"/>
       <c r="G58" s="1"/>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="4"/>
+      <c r="C59" s="4">
+        <v>1</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F59" s="4"/>
       <c r="G59" s="1"/>
-      <c r="I59" s="5"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F60" s="4"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <v>5</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E61" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F61" s="4"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <v>2</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F62" s="4"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>54</v>
-      </c>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="4"/>
       <c r="B63" s="4"/>
-      <c r="C63" s="4">
-        <v>5</v>
-      </c>
+      <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
@@ -2665,194 +2960,294 @@
       <c r="F64" s="4"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
+      <c r="E65" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F65" s="4"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>41</v>
+      </c>
       <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
+      <c r="C66" s="4">
+        <v>3</v>
+      </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
+      <c r="B67" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
+      <c r="E67" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F67" s="4"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="4"/>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>42</v>
+      </c>
       <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="7"/>
+      <c r="C68" s="4">
+        <v>2</v>
+      </c>
+      <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="4"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7" ht="71" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>43</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4">
+        <v>3</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="C70" s="4"/>
-      <c r="D70" s="6"/>
+      <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="6"/>
+      <c r="F70" s="4"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>44</v>
+      </c>
       <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
+      <c r="C71" s="4">
+        <v>3</v>
+      </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="4"/>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>45</v>
+      </c>
       <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
+      <c r="C72" s="4">
+        <v>5</v>
+      </c>
       <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F72" s="4"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
+      <c r="B73" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F73" s="4"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
+        <v>46</v>
+      </c>
       <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
+      <c r="C74" s="4">
+        <v>2</v>
+      </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
+      <c r="B75" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F75" s="4"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>47</v>
+      </c>
       <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
+      <c r="C76" s="4">
+        <v>5</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F76" s="4"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="4"/>
+    <row r="77" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4">
+        <v>48</v>
+      </c>
       <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="C77" s="4">
+        <v>2</v>
+      </c>
       <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
+      <c r="E77" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F77" s="4"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="4"/>
+    <row r="78" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="4">
+        <v>49</v>
+      </c>
       <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
+      <c r="C78" s="4">
+        <v>5</v>
+      </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="4"/>
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4">
+        <v>50</v>
+      </c>
       <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
+      <c r="C79" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="1"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
+      <c r="I79" s="5"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="4">
+        <v>51</v>
+      </c>
       <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="7"/>
+      <c r="C80" s="4">
+        <v>2</v>
+      </c>
+      <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="7"/>
+      <c r="F80" s="4"/>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
+      <c r="A81" s="4">
+        <v>52</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4">
+        <v>5</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
+      <c r="A82" s="4">
+        <v>53</v>
+      </c>
       <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="6"/>
+      <c r="C82" s="4">
+        <v>2</v>
+      </c>
+      <c r="D82" s="4"/>
       <c r="E82" s="4"/>
-      <c r="F82" s="6"/>
+      <c r="F82" s="4"/>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
+      <c r="A83" s="4">
+        <v>54</v>
+      </c>
       <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
+      <c r="C83" s="4">
+        <v>5</v>
+      </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="4"/>
+      <c r="A84" s="4">
+        <v>55</v>
+      </c>
       <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
+      <c r="C84" s="4">
+        <v>2</v>
+      </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="4"/>
+      <c r="A85" s="4">
+        <v>56</v>
+      </c>
       <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
+      <c r="C85" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
@@ -2880,27 +3275,27 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="1"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="1:7" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -2988,24 +3383,204 @@
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
       <c r="G100" s="1"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="1"/>
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="1"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="1"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="1"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G101" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:G121" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="F70:F80 F82:F101 D82:D101 D70:D80 F4:F68 D4:D68" xr:uid="{4167D8AB-A9F7-D14C-A73B-128325BA2547}">
+    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D102:F121 D90:F100 D4:F88" xr:uid="{4167D8AB-A9F7-D14C-A73B-128325BA2547}">
       <formula1>judgment_options</formula1>
     </dataValidation>
   </dataValidations>
@@ -3016,14 +3591,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2A33D0-7CAD-4042-B770-9D7FC78063D3}">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="40.33203125" customWidth="1"/>
   </cols>
@@ -3074,7 +3647,9 @@
       <c r="D4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
@@ -3090,7 +3665,9 @@
       <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
@@ -3106,7 +3683,9 @@
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
@@ -3125,7 +3704,9 @@
       <c r="D7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="1"/>
     </row>
@@ -3138,7 +3719,9 @@
         <v>20</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="1"/>
     </row>
@@ -3153,7 +3736,9 @@
       <c r="D9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="1"/>
     </row>
@@ -3168,7 +3753,9 @@
       <c r="D10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="1"/>
     </row>
@@ -3183,7 +3770,9 @@
       <c r="D11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="1"/>
     </row>
@@ -3198,30 +3787,32 @@
       <c r="D12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4">
-        <v>2</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -3230,11 +3821,11 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -3243,39 +3834,39 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
-        <v>4</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="4">
-        <v>3</v>
+      <c r="C18" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -3284,39 +3875,39 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
-        <v>4</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
-        <v>20</v>
+      <c r="C21" s="4">
+        <v>2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -3325,11 +3916,11 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="4">
-        <v>3</v>
+      <c r="C22" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -3338,11 +3929,11 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -3351,54 +3942,54 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
-        <v>4</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="4"/>
+      <c r="A25" s="4">
+        <v>18</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4">
+        <v>4</v>
+      </c>
       <c r="D25" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
-        <v>19</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A27" s="4">
+        <v>19</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="1"/>
@@ -3406,36 +3997,36 @@
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
-        <v>20</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -3444,11 +4035,11 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -3457,11 +4048,11 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -3469,38 +4060,38 @@
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A33" s="4">
+        <v>23</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4">
+        <v>3</v>
+      </c>
+      <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
-        <v>24</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4">
-        <v>5</v>
-      </c>
-      <c r="D34" s="4"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -3509,11 +4100,11 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="4" t="s">
-        <v>20</v>
+      <c r="C36" s="4">
+        <v>2</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -3522,24 +4113,26 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="4">
-        <v>5</v>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F37" s="4"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -3547,14 +4140,14 @@
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A39" s="4">
+        <v>28</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4">
+        <v>3</v>
+      </c>
+      <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="1"/>
@@ -3562,11 +4155,11 @@
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -3575,7 +4168,7 @@
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
@@ -3586,25 +4179,25 @@
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>29</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4">
-        <v>2</v>
-      </c>
-      <c r="D42" s="4"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
-        <v>20</v>
+      <c r="C43" s="4">
+        <v>2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3613,11 +4206,11 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="4">
-        <v>2</v>
+      <c r="C44" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3625,38 +4218,40 @@
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="4"/>
+      <c r="A45" s="4">
+        <v>31</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F45" s="4"/>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4">
-        <v>5</v>
-      </c>
-      <c r="D46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" s="4"/>
-      <c r="C47" s="4" t="s">
-        <v>20</v>
+      <c r="C47" s="4">
+        <v>5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -3664,53 +4259,53 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4" t="s">
+      <c r="A48" s="4">
         <v>33</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F48" s="4"/>
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
-        <v>34</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4">
-        <v>3</v>
-      </c>
-      <c r="D49" s="4"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <v>1</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>5</v>
@@ -3721,65 +4316,67 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <v>1</v>
-      </c>
-      <c r="D52" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <v>4</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54" s="4"/>
+      <c r="A54" s="4">
+        <v>38</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4">
+        <v>4</v>
+      </c>
       <c r="D54" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
-        <v>39</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4">
-        <v>2</v>
-      </c>
-      <c r="D55" s="4"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3788,11 +4385,11 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
-        <v>20</v>
+      <c r="C57" s="4">
+        <v>3</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3801,67 +4398,73 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="4">
-        <v>4</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="4"/>
+      <c r="C58" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F58" s="4"/>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <v>3</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="F59" s="4"/>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <v>5</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F60" s="4"/>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <v>2</v>
-      </c>
-      <c r="D61" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -3870,7 +4473,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
@@ -3881,28 +4484,26 @@
       <c r="F63" s="4"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <v>4</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>3</v>
@@ -3910,58 +4511,58 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="1"/>
-      <c r="I65" s="3"/>
     </row>
     <row r="66" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <v>2</v>
-      </c>
-      <c r="D66" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="1"/>
-      <c r="I66" s="5"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="1"/>
+      <c r="I67" s="5"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A68" s="4">
+        <v>51</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4">
+        <v>3</v>
+      </c>
+      <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>52</v>
-      </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" s="4"/>
       <c r="D69" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
@@ -3969,24 +4570,28 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B70" s="4"/>
-      <c r="C70" s="4">
-        <v>1</v>
-      </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="C70" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F70" s="4"/>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -3995,34 +4600,42 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B72" s="4"/>
-      <c r="C72" s="4" t="s">
-        <v>20</v>
+      <c r="C72" s="4">
+        <v>3</v>
       </c>
       <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F72" s="4"/>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F73" s="4"/>
       <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
+      <c r="A74" s="4">
+        <v>56</v>
+      </c>
       <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
+      <c r="C74" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
@@ -4032,36 +4645,36 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="7"/>
+      <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="7"/>
+      <c r="F75" s="4"/>
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="1"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -4140,36 +4753,36 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="7"/>
+      <c r="D87" s="4"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="7"/>
+      <c r="F87" s="4"/>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="1"/>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -4334,10 +4947,19 @@
       <c r="F108" s="4"/>
       <c r="G108" s="1"/>
     </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G108" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:G109" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="F77:F87 F89:F108 D71 F4:F75 D4:D70 D72:D75 D77:D87 D89:D108" xr:uid="{22824E97-1CE6-E643-88BC-327E953CE45A}">
+    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D78:F88 D90:F109 D4:F76" xr:uid="{22824E97-1CE6-E643-88BC-327E953CE45A}">
       <formula1>judgment_options</formula1>
     </dataValidation>
   </dataValidations>

--- a/MERIX SUBMISSION/M06-2_XML_WebViz/exports/score_pdf_long/pdf/评估/乐句断句评审表.xlsx
+++ b/MERIX SUBMISSION/M06-2_XML_WebViz/exports/score_pdf_long/pdf/评估/乐句断句评审表.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toddywang/Documents/VsCodeProjects/xmltoexp/MERIX SUBMISSION/M06-2_XML_WebViz/exports/score_pdf_long/pdf/评估/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84DBAAD-CA27-5A47-92AB-15F4436BD2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCB2BC0-C4A2-CC4A-B587-819F5E96A83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20580" yWindow="500" windowWidth="17820" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="选项" sheetId="2" r:id="rId1"/>
     <sheet name="M06-1" sheetId="14" r:id="rId2"/>
     <sheet name="M06-2" sheetId="16" r:id="rId3"/>
     <sheet name="M06-3" sheetId="17" r:id="rId4"/>
+    <sheet name="k283" sheetId="18" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'M06-1'!$A$3:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'M06-1'!$A$3:$G$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'M06-2'!$A$3:$G$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'M06-3'!$A$3:$G$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'M06-3'!$A$3:$G$110</definedName>
     <definedName name="judgment_options">选项!$A$2:$A$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="74">
   <si>
     <t>判断</t>
   </si>
@@ -247,6 +248,30 @@
   </si>
   <si>
     <t>m10b1</t>
+  </si>
+  <si>
+    <t>m7b1</t>
+  </si>
+  <si>
+    <t>m103b1</t>
+  </si>
+  <si>
+    <t>m104b1</t>
+  </si>
+  <si>
+    <t>m105b1</t>
+  </si>
+  <si>
+    <t>m5b1</t>
+  </si>
+  <si>
+    <t>m33b3</t>
+  </si>
+  <si>
+    <t>m85b1</t>
+  </si>
+  <si>
+    <t>m112b1</t>
   </si>
 </sst>
 </file>
@@ -313,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -335,6 +360,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -669,7 +697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E874A1B1-FC00-764C-9222-91C2AE8AA66D}">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -804,153 +832,161 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>3</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4">
-        <v>3</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="4">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>5</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4">
-        <v>3</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="4">
+        <v>5</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4">
-        <v>1</v>
-      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="4"/>
+      <c r="A15" s="4">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>7</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4">
-        <v>3</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <v>5</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="4">
+        <v>8</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
-        <v>9</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
+      <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -958,177 +994,184 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
+        <v>10</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>11</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
-        <v>12</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="4"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="4">
+        <v>12</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
-        <v>13</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>14</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
         <v>1</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
-        <v>15</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4">
-        <v>3</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F28" s="4"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <v>4</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
@@ -1141,7 +1184,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4">
@@ -1154,114 +1197,120 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="4" t="s">
-        <v>20</v>
+      <c r="C34" s="4">
+        <v>3</v>
       </c>
       <c r="D34" s="4"/>
-      <c r="E34" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
+        <v>21</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
         <v>22</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4">
+        <v>3</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
-        <v>23</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4">
-        <v>3</v>
-      </c>
+      <c r="C37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F37" s="4"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C38" s="4">
+        <v>3</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="4"/>
-      <c r="C39" s="4">
-        <v>3</v>
+      <c r="C39" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="4"/>
+      <c r="C40" s="4">
+        <v>3</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="4">
-        <v>3</v>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -1270,39 +1319,39 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <v>5</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <v>4</v>
-      </c>
-      <c r="D43" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -1311,7 +1360,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
@@ -1324,7 +1373,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
@@ -1336,83 +1385,79 @@
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A47" s="4">
+        <v>32</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4">
+        <v>3</v>
+      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
-        <v>33</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4">
-        <v>3</v>
-      </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <v>1</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <v>3</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F50" s="4"/>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="C51" s="4">
+        <v>3</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
@@ -1424,82 +1469,88 @@
       <c r="E52" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
+        <v>37</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="4">
         <v>38</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4">
-        <v>3</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4">
+        <v>3</v>
+      </c>
       <c r="D54" s="4"/>
-      <c r="E54" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
-        <v>39</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4">
-        <v>3</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="4"/>
       <c r="D55" s="4"/>
-      <c r="F55" s="4"/>
+      <c r="E55" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <v>5</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E56" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
-        <v>20</v>
+      <c r="C57" s="4">
+        <v>5</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
@@ -1511,56 +1562,61 @@
       <c r="E58" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="F58" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="4">
-        <v>5</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="C59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
         <v>5</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="4"/>
-      <c r="C61" s="4" t="s">
-        <v>20</v>
+      <c r="C61" s="4">
+        <v>5</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
@@ -1572,195 +1628,224 @@
       <c r="E62" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
+        <v>46</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
         <v>47</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4">
-        <v>5</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>48</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <v>4</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
         <v>4</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G65" s="1"/>
-      <c r="I65" s="3"/>
     </row>
     <row r="66" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
+      <c r="A66" s="4">
+        <v>49</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4">
+        <v>4</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E66" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="4"/>
+        <v>5</v>
+      </c>
       <c r="G66" s="1"/>
       <c r="I66" s="3"/>
     </row>
     <row r="67" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>50</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4">
-        <v>3</v>
-      </c>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="4"/>
       <c r="D67" s="4"/>
+      <c r="E67" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F67" s="4"/>
       <c r="G67" s="1"/>
-      <c r="I67" s="5"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
         <v>3</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E68" s="4"/>
+      <c r="D68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>52</v>
-      </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4">
-        <v>1</v>
-      </c>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" s="4"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+      <c r="F69" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>53</v>
-      </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4">
-        <v>3</v>
-      </c>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="4"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+      <c r="F70" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>54</v>
-      </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4">
-        <v>1</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="I70" s="5"/>
+    </row>
+    <row r="71" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="F71" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="G71" s="1"/>
+      <c r="I71" s="5"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B72" s="4"/>
-      <c r="C72" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" s="4"/>
+      <c r="C72" s="4">
+        <v>3</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="4"/>
+      <c r="A73" s="4">
+        <v>52</v>
+      </c>
       <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
+      <c r="C73" s="4">
+        <v>1</v>
+      </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
+      <c r="F73" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
+      <c r="A74" s="4">
+        <v>53</v>
+      </c>
       <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
+      <c r="C74" s="4">
+        <v>3</v>
+      </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
+      <c r="A75" s="4">
+        <v>54</v>
+      </c>
       <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
+      <c r="C75" s="4">
+        <v>1</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>55</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -1776,27 +1861,27 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="1"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="1:7" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
@@ -1848,27 +1933,27 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -1884,27 +1969,27 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="1"/>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -2042,10 +2127,46 @@
       <c r="F108" s="4"/>
       <c r="G108" s="1"/>
     </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G108" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:G112" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D89:F108 D77:F87 D4:E54 F4:F57 E64:E66 D56:E63 D55 D68:E75 D64:D67 F59:F75" xr:uid="{C4C596A4-9E85-914E-B561-DE7166F64426}">
+    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D93:F112 D81:F91 D4:E55 E65:E67 D57:E64 D56 D72:E79 D65:D71 F4:F30 F32:F64 F66:F79" xr:uid="{C4C596A4-9E85-914E-B561-DE7166F64426}">
       <formula1>judgment_options</formula1>
     </dataValidation>
   </dataValidations>
@@ -2222,7 +2343,9 @@
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -2267,7 +2390,9 @@
       <c r="E14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -2340,7 +2465,9 @@
       <c r="E19" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -2353,7 +2480,9 @@
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -2461,7 +2590,9 @@
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -2476,7 +2607,9 @@
       <c r="E29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -2489,7 +2622,9 @@
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -2549,7 +2684,9 @@
       <c r="E34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -2935,7 +3072,9 @@
       <c r="E62" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
@@ -3123,7 +3262,9 @@
       <c r="E76" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -3198,7 +3339,9 @@
       <c r="E81" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F81" s="4"/>
+      <c r="F81" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
@@ -3591,7 +3734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2A33D0-7CAD-4042-B770-9D7FC78063D3}">
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -3707,7 +3850,9 @@
       <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -3722,7 +3867,9 @@
       <c r="E8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -3739,33 +3886,31 @@
       <c r="E9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4">
-        <v>2</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="4"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
+      <c r="C11" s="4">
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>5</v>
@@ -3778,54 +3923,60 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="4">
-        <v>4</v>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="4">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4">
-        <v>2</v>
-      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -3834,11 +3985,11 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -3847,39 +3998,39 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <v>4</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="4"/>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="4">
-        <v>3</v>
+      <c r="C19" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -3888,39 +4039,39 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <v>4</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
-        <v>2</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
-        <v>20</v>
+      <c r="C22" s="4">
+        <v>2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -3929,80 +4080,81 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="4">
-        <v>3</v>
+      <c r="C23" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
-        <v>4</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="4"/>
+      <c r="A26" s="4">
+        <v>18</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4">
+        <v>4</v>
+      </c>
       <c r="D26" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
-        <v>19</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A28" s="4">
+        <v>19</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="1"/>
@@ -4010,36 +4162,36 @@
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
-        <v>20</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -4048,11 +4200,11 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -4061,11 +4213,11 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -4073,38 +4225,38 @@
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A34" s="4">
+        <v>23</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4">
+        <v>3</v>
+      </c>
+      <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
-        <v>24</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4">
-        <v>5</v>
-      </c>
-      <c r="D35" s="4"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -4113,39 +4265,39 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="4" t="s">
-        <v>20</v>
+      <c r="C37" s="4">
+        <v>2</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="4">
-        <v>5</v>
+      <c r="C38" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -4153,14 +4305,14 @@
       <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A40" s="4">
+        <v>28</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4">
+        <v>3</v>
+      </c>
+      <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="1"/>
@@ -4168,11 +4320,11 @@
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -4181,7 +4333,7 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
@@ -4192,25 +4344,25 @@
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
-        <v>29</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4">
-        <v>2</v>
-      </c>
-      <c r="D43" s="4"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="4" t="s">
-        <v>20</v>
+      <c r="C44" s="4">
+        <v>2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -4219,108 +4371,108 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="4"/>
-      <c r="C45" s="4">
-        <v>2</v>
+      <c r="C45" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="4"/>
+      <c r="A46" s="4">
+        <v>31</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4">
+        <v>2</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F46" s="4"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4">
-        <v>5</v>
-      </c>
-      <c r="D47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="4" t="s">
-        <v>20</v>
+      <c r="C48" s="4">
+        <v>5</v>
       </c>
       <c r="D48" s="4"/>
-      <c r="E48" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4" t="s">
+      <c r="A49" s="4">
         <v>33</v>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
-        <v>34</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4">
-        <v>3</v>
-      </c>
-      <c r="D50" s="4"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <v>1</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>5</v>
@@ -4331,65 +4483,67 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="D53" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <v>4</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C55" s="4"/>
+      <c r="A55" s="4">
+        <v>38</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4">
+        <v>4</v>
+      </c>
       <c r="D55" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
-        <v>39</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4">
-        <v>2</v>
-      </c>
-      <c r="D56" s="4"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -4398,86 +4552,88 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="4" t="s">
-        <v>20</v>
+      <c r="C58" s="4">
+        <v>3</v>
       </c>
       <c r="D58" s="4"/>
-      <c r="E58" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="4">
-        <v>4</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="C59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="4"/>
       <c r="E59" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <v>3</v>
-      </c>
-      <c r="D60" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <v>5</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E61" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="F61" s="4"/>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <v>2</v>
-      </c>
-      <c r="D62" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -4486,7 +4642,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
@@ -4497,28 +4653,26 @@
       <c r="F64" s="4"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <v>4</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>3</v>
@@ -4526,100 +4680,102 @@
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="1"/>
-      <c r="I66" s="3"/>
     </row>
     <row r="67" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <v>2</v>
-      </c>
-      <c r="D67" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="1"/>
-      <c r="I67" s="5"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="1"/>
+      <c r="I68" s="5"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A69" s="4">
+        <v>51</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4">
+        <v>3</v>
+      </c>
+      <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>52</v>
-      </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" s="4"/>
       <c r="D70" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B71" s="4"/>
-      <c r="C71" s="4">
-        <v>1</v>
-      </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="C71" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" s="4"/>
-      <c r="E72" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B73" s="4"/>
-      <c r="C73" s="4" t="s">
-        <v>20</v>
+      <c r="C73" s="4">
+        <v>3</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
@@ -4630,21 +4786,29 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>56</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
@@ -4654,36 +4818,36 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -4762,36 +4926,36 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="1"/>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
@@ -4956,14 +5120,1832 @@
       <c r="F109" s="4"/>
       <c r="G109" s="1"/>
     </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G109" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:G110" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D78:F88 D90:F109 D4:F76" xr:uid="{22824E97-1CE6-E643-88BC-327E953CE45A}">
+    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="D79:F89 D91:F110 F23 D4:F22 D25:F77 D23:E24" xr:uid="{22824E97-1CE6-E643-88BC-327E953CE45A}">
       <formula1>judgment_options</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5A5543-BD07-D641-B1B6-13AF9B450135}">
+  <dimension ref="A1:I121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="40.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>9</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>10</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>11</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>13</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>14</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>15</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>16</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4">
+        <v>5</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>17</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
+        <v>18</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>19</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>20</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>21</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>22</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>23</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4">
+        <v>3</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>24</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
+        <v>25</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4">
+        <v>3</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>26</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4">
+        <v>2</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>27</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4">
+        <v>5</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <v>28</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>29</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4">
+        <v>2</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>30</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4">
+        <v>3</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4">
+        <v>5</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>32</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
+        <v>33</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4">
+        <v>4</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <v>34</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4">
+        <v>3</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
+        <v>35</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4">
+        <v>5</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
+        <v>36</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4">
+        <v>2</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
+        <v>37</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4">
+        <v>3</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
+        <v>38</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
+        <v>39</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4">
+        <v>5</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="4">
+        <v>40</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4">
+        <v>3</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="4">
+        <v>41</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4">
+        <v>5</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
+        <v>42</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4">
+        <v>3</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="4">
+        <v>43</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="4">
+        <v>44</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4">
+        <v>3</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="4">
+        <v>45</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4">
+        <v>3</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="4">
+        <v>46</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4">
+        <v>2</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="4">
+        <v>47</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4">
+        <v>3</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4">
+        <v>48</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4">
+        <v>2</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
+        <v>49</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4">
+        <v>3</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>50</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4">
+        <v>5</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="1"/>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>51</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4">
+        <v>3</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>52</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4">
+        <v>5</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>53</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4">
+        <v>5</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>54</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4">
+        <v>2</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>55</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4">
+        <v>3</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>56</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4">
+        <v>5</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>57</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4">
+        <v>3</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>58</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4">
+        <v>2</v>
+      </c>
+      <c r="D66" s="7"/>
+      <c r="E66" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="7"/>
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>59</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4">
+        <v>3</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>60</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4">
+        <v>5</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>61</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4">
+        <v>2</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>62</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4">
+        <v>5</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="1"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G71" s="1"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>63</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4">
+        <v>2</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="1"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>64</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4">
+        <v>5</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G73" s="1"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
+        <v>65</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4">
+        <v>2</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>66</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4">
+        <v>3</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="1"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>67</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4">
+        <v>2</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="4">
+        <v>68</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4">
+        <v>5</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="4">
+        <v>69</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4">
+        <v>3</v>
+      </c>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="1"/>
+    </row>
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A79" s="4">
+        <v>70</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G79" s="1"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="4">
+        <v>71</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4">
+        <v>3</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="4">
+        <v>72</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4">
+        <v>5</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="4">
+        <v>73</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4">
+        <v>3</v>
+      </c>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="4">
+        <v>74</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4">
+        <v>3</v>
+      </c>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="1"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="4">
+        <v>75</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="1"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="4">
+        <v>76</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4">
+        <v>3</v>
+      </c>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G85" s="1"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="4">
+        <v>77</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4">
+        <v>3</v>
+      </c>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="1"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="4">
+        <v>78</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4">
+        <v>2</v>
+      </c>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="1"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="4">
+        <v>79</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G88" s="1"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="4">
+        <v>80</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4">
+        <v>5</v>
+      </c>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="1"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="4">
+        <v>81</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4">
+        <v>3</v>
+      </c>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="1"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="4">
+        <v>82</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4">
+        <v>5</v>
+      </c>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="1"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="4">
+        <v>83</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="1"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="4">
+        <v>84</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4">
+        <v>5</v>
+      </c>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="1"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="4">
+        <v>85</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4">
+        <v>2</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="1"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="4">
+        <v>86</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4">
+        <v>2</v>
+      </c>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="4">
+        <v>87</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4">
+        <v>3</v>
+      </c>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="1"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="4">
+        <v>88</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4">
+        <v>5</v>
+      </c>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G97" s="1"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="4">
+        <v>89</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4">
+        <v>3</v>
+      </c>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="1"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="4">
+        <v>90</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4">
+        <v>3</v>
+      </c>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="1"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="4">
+        <v>91</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4">
+        <v>5</v>
+      </c>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="1"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="4">
+        <v>92</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4">
+        <v>2</v>
+      </c>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="1"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="4">
+        <v>93</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="4">
+        <v>94</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4">
+        <v>4</v>
+      </c>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="4">
+        <v>95</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4">
+        <v>3</v>
+      </c>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="4">
+        <v>96</v>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4">
+        <v>5</v>
+      </c>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="4">
+        <v>97</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4">
+        <v>2</v>
+      </c>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="4">
+        <v>98</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="4">
+        <v>99</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4">
+        <v>3</v>
+      </c>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="4">
+        <v>100</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="4">
+        <v>101</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4">
+        <v>2</v>
+      </c>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="4">
+        <v>102</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4">
+        <v>5</v>
+      </c>
+      <c r="D112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="4">
+        <v>103</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4">
+        <v>3</v>
+      </c>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G113" s="1"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="4">
+        <v>104</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4">
+        <v>2</v>
+      </c>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="4">
+        <v>105</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4">
+        <v>5</v>
+      </c>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="4">
+        <v>106</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4">
+        <v>2</v>
+      </c>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="4">
+        <v>107</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4">
+        <v>2</v>
+      </c>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="4">
+        <v>108</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4">
+        <v>3</v>
+      </c>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G119" s="1"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="4">
+        <v>109</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4">
+        <v>3</v>
+      </c>
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="1"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="4">
+        <v>110</v>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4">
+        <v>2</v>
+      </c>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="1"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" error="只能从下拉选项中选择。" prompt="请选择：应断 / 可断可不断 / 不应断" sqref="F22 D21:E22 D113:E114 D4:F20 D115:F121 E50 D23:F49 D50:D51 F50:F51 E111 D52:F110 D111:D112 F111:F113" xr:uid="{6976C979-2A6B-3248-97D5-CD36ACD7ADBC}">
+      <formula1>judgment_options</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>